--- a/data/trans_camb/IP1017-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1017-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
